--- a/reports/Debug-snowbowl-20260105/Month to Date (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/Month to Date (Actual)_Revenue.xlsx
@@ -642,7 +642,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="2">
-        <v>128510.1600</v>
+        <v>128531.7100</v>
       </c>
     </row>
     <row r="14" spans="1:4">
